--- a/event_02/forms/travel_support.xlsx
+++ b/event_02/forms/travel_support.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\notom\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6368A73-E743-4E30-AA05-81F581BCD835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246822CE-D78B-411C-8BB1-BCF524A09077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11130" yWindow="21600" windowWidth="14610" windowHeight="15585" xr2:uid="{DDB6597E-3996-4D4F-849A-44848E240032}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{DDB6597E-3996-4D4F-849A-44848E240032}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>銀行名</t>
     <rPh sb="0" eb="3">
@@ -347,6 +347,19 @@
   </si>
   <si>
     <t>以下のすべての条件に該当する方のみ、旅費支援の対象となります。確認の上、チェック（□⇒■）してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第２回システム行動学研究会で、ポスター発表をする方</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="7" eb="13">
+      <t>コウドウガクケンキュウカイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -487,7 +500,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -518,20 +531,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -895,7 +905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0DBBF6F-9296-F54F-A8A4-8B40C9AAA8FF}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -908,17 +918,17 @@
     <col min="9" max="9" width="39.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="60.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:9" ht="60.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
-    <row r="2" spans="1:12" ht="45.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="45.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -943,11 +953,8 @@
       <c r="I2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
     </row>
-    <row r="3" spans="1:12" ht="57.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="57.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -972,11 +979,8 @@
       <c r="H3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
     </row>
-    <row r="4" spans="1:12" ht="63.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" ht="63.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -987,22 +991,19 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
+      <c r="I4" s="10"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>16</v>
       </c>
@@ -1010,20 +1011,28 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/event_02/forms/travel_support.xlsx
+++ b/event_02/forms/travel_support.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\notom\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246822CE-D78B-411C-8BB1-BCF524A09077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D6F5F7-8D02-4A17-83C0-E07EC52A0F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{DDB6597E-3996-4D4F-849A-44848E240032}"/>
+    <workbookView xWindow="240" yWindow="525" windowWidth="38700" windowHeight="15345" xr2:uid="{DDB6597E-3996-4D4F-849A-44848E240032}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -310,31 +310,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>旅費支援が研究費等による支給と重複しないこと</t>
-    <rPh sb="0" eb="2">
-      <t>リョヒ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シエン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ケンキュウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シキュウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジュウフク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>愛知県外に在住していること</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -359,6 +334,31 @@
     </rPh>
     <rPh sb="7" eb="13">
       <t>コウドウガクケンキュウカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自身で研究費を持たず、旅費支援が研究費等による支給と重複しないこと</t>
+    <rPh sb="11" eb="13">
+      <t>リョヒ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シエン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケンキュウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シキュウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ジュウフク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
@@ -1008,7 +1008,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
@@ -1016,7 +1016,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -1024,7 +1024,7 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -1032,7 +1032,7 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
